--- a/kirill/reference/PPlay1.xlsx
+++ b/kirill/reference/PPlay1.xlsx
@@ -19,10 +19,10 @@
     <t>PPlay1 of uriel (Reporter)</t>
   </si>
   <si>
-    <t>��������� 16 ������ 2026 08:39:53</t>
-  </si>
-  <si>
-    <t>16/08/2026 08:39:53</t>
+    <t>������� 17 ������ 2026 11:27:36</t>
+  </si>
+  <si>
+    <t>17/08/2026 11:27:36</t>
   </si>
   <si>
     <t>2026/Aug,Months,Companies,Customers,Items,������,Areas,Agents by Customers,�������,Agents,���</t>
@@ -34,13 +34,13 @@
     <t>Customers</t>
   </si>
   <si>
-    <t>� 401,144.5</t>
+    <t>� 406,049.2</t>
   </si>
   <si>
     <t>0��� �����</t>
   </si>
   <si>
-    <t>� 63,348.3</t>
+    <t>� 66,234.1</t>
   </si>
   <si>
     <t>0����� ����</t>
@@ -52,7 +52,7 @@
     <t>0������</t>
   </si>
   <si>
-    <t>� 292,490.7</t>
+    <t>� 293,547.5</t>
   </si>
   <si>
     <t>���� BE</t>
@@ -88,13 +88,13 @@
     <t>������ BE</t>
   </si>
   <si>
-    <t>� 38,184.6</t>
+    <t>� 39,241.4</t>
   </si>
   <si>
     <t>0����� �����</t>
   </si>
   <si>
-    <t>� 45,091.6</t>
+    <t>� 46,053.6</t>
   </si>
 </sst>
 </file>
